--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{553E1F6C-B83E-4958-B2C6-24F6E7CC5889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0C661B-1F10-4D4F-9CC7-7EC720DC19FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -224,6 +224,9 @@
   </si>
   <si>
     <t>It was a intersting day.</t>
+  </si>
+  <si>
+    <t>happy day</t>
   </si>
 </sst>
 </file>
@@ -1233,26 +1236,50 @@
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="13"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15" t="str">
+      <c r="A11" s="13">
+        <v>46259</v>
+      </c>
+      <c r="B11" s="14">
+        <v>300</v>
+      </c>
+      <c r="C11" s="14">
+        <v>20</v>
+      </c>
+      <c r="D11" s="14">
+        <v>45</v>
+      </c>
+      <c r="E11" s="14">
+        <v>40</v>
+      </c>
+      <c r="F11" s="14">
+        <v>250</v>
+      </c>
+      <c r="G11" s="14">
+        <v>5</v>
+      </c>
+      <c r="H11" s="14">
+        <v>60</v>
+      </c>
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J11" s="15" t="str">
+        <v>715</v>
+      </c>
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="17"/>
+        <v>725</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N11" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A0C661B-1F10-4D4F-9CC7-7EC720DC19FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B19A75-AAE6-4277-9AFE-2407658478F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -227,6 +227,9 @@
   </si>
   <si>
     <t>happy day</t>
+  </si>
+  <si>
+    <t>cheerful day</t>
   </si>
 </sst>
 </file>
@@ -1282,26 +1285,50 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="13"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15" t="str">
+      <c r="A12" s="13">
+        <v>46260</v>
+      </c>
+      <c r="B12" s="14">
+        <v>300</v>
+      </c>
+      <c r="C12" s="14">
+        <v>30</v>
+      </c>
+      <c r="D12" s="14">
+        <v>40</v>
+      </c>
+      <c r="E12" s="14">
+        <v>40</v>
+      </c>
+      <c r="F12" s="14">
+        <v>250</v>
+      </c>
+      <c r="G12" s="14">
+        <v>5</v>
+      </c>
+      <c r="H12" s="14">
+        <v>70</v>
+      </c>
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J12" s="15" t="str">
+        <v>730</v>
+      </c>
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="17"/>
+        <v>710</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L12" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N12" s="17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B19A75-AAE6-4277-9AFE-2407658478F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974BB2C4-E9FC-4EDA-AD55-71A5A3E5152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>cheerful day</t>
+  </si>
+  <si>
+    <t>feeling happy and positive</t>
   </si>
 </sst>
 </file>
@@ -1331,26 +1334,50 @@
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="13"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15" t="str">
+      <c r="A13" s="13">
+        <v>46261</v>
+      </c>
+      <c r="B13" s="14">
+        <v>310</v>
+      </c>
+      <c r="C13" s="14">
+        <v>20</v>
+      </c>
+      <c r="D13" s="14">
+        <v>50</v>
+      </c>
+      <c r="E13" s="14">
+        <v>50</v>
+      </c>
+      <c r="F13" s="14">
+        <v>300</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6</v>
+      </c>
+      <c r="H13" s="14">
+        <v>40</v>
+      </c>
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J13" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" s="16"/>
-      <c r="N13" s="17"/>
+        <v>670</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N13" s="17" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974BB2C4-E9FC-4EDA-AD55-71A5A3E5152E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA0A68C-60BA-4D25-AEAF-785FAC0A3D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>feeling happy and positive</t>
+  </si>
+  <si>
+    <t>2026-08--28</t>
+  </si>
+  <si>
+    <t>stressful day</t>
   </si>
 </sst>
 </file>
@@ -1380,26 +1386,50 @@
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="13"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15" t="str">
+      <c r="A14" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B14" s="14">
+        <v>350</v>
+      </c>
+      <c r="C14" s="14">
+        <v>30</v>
+      </c>
+      <c r="D14" s="14">
+        <v>40</v>
+      </c>
+      <c r="E14" s="14">
+        <v>50</v>
+      </c>
+      <c r="F14" s="14">
+        <v>200</v>
+      </c>
+      <c r="G14" s="14">
+        <v>4</v>
+      </c>
+      <c r="H14" s="14">
+        <v>70</v>
+      </c>
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J14" s="15" t="str">
+        <v>740</v>
+      </c>
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" s="16"/>
-      <c r="N14" s="17"/>
+        <v>700</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M14" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N14" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAA0A68C-60BA-4D25-AEAF-785FAC0A3D3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DACF5B8-642F-4E7B-8075-7D9FE7B9D8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1432,26 +1432,50 @@
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="13"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="str">
+      <c r="A15" s="13">
+        <v>46263</v>
+      </c>
+      <c r="B15" s="14">
+        <v>390</v>
+      </c>
+      <c r="C15" s="14">
+        <v>30</v>
+      </c>
+      <c r="D15" s="14">
+        <v>50</v>
+      </c>
+      <c r="E15" s="14">
+        <v>30</v>
+      </c>
+      <c r="F15" s="14">
+        <v>0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>0</v>
+      </c>
+      <c r="H15" s="14">
+        <v>70</v>
+      </c>
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J15" s="15" t="str">
+        <v>570</v>
+      </c>
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" s="16"/>
-      <c r="N15" s="17"/>
+        <v>870</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="M15" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N15" s="17" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DACF5B8-642F-4E7B-8075-7D9FE7B9D8C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1201C4E4-E09A-4302-A12C-F7F388DE0D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>stressful day</t>
+  </si>
+  <si>
+    <t>Unsatisfied</t>
+  </si>
+  <si>
+    <t>low energy and felt tired</t>
   </si>
 </sst>
 </file>
@@ -1478,26 +1484,50 @@
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="13"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="str">
+      <c r="A16" s="13">
+        <v>46264</v>
+      </c>
+      <c r="B16" s="14">
+        <v>480</v>
+      </c>
+      <c r="C16" s="14">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>50</v>
+      </c>
+      <c r="E16" s="14">
+        <v>50</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
+      </c>
+      <c r="H16" s="14">
+        <v>80</v>
+      </c>
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J16" s="15" t="str">
+        <v>680</v>
+      </c>
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" s="16"/>
-      <c r="N16" s="17"/>
+        <v>760</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="17" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1201C4E4-E09A-4302-A12C-F7F388DE0D68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A15DFB7-C5E9-4F53-A6AF-E400966F444F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="74">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>low energy and felt tired</t>
+  </si>
+  <si>
+    <t>feeling happy and relaxed</t>
   </si>
 </sst>
 </file>
@@ -1530,26 +1533,50 @@
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="13"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15" t="str">
+      <c r="A17" s="13">
+        <v>46265</v>
+      </c>
+      <c r="B17" s="14">
+        <v>300</v>
+      </c>
+      <c r="C17" s="14">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
+        <v>60</v>
+      </c>
+      <c r="E17" s="14">
+        <v>60</v>
+      </c>
+      <c r="F17" s="14">
+        <v>100</v>
+      </c>
+      <c r="G17" s="14">
+        <v>2</v>
+      </c>
+      <c r="H17" s="14">
+        <v>90</v>
+      </c>
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J17" s="15" t="str">
+        <v>630</v>
+      </c>
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" s="16"/>
-      <c r="N17" s="17"/>
+        <v>810</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L17" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M17" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A15DFB7-C5E9-4F53-A6AF-E400966F444F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91A70D7-3656-47DE-AFD9-1AF7E835247F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t>feeling happy and relaxed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">An average day </t>
   </si>
 </sst>
 </file>
@@ -1579,26 +1582,50 @@
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="13"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15" t="str">
+      <c r="A18" s="13">
+        <v>46266</v>
+      </c>
+      <c r="B18" s="14">
+        <v>360</v>
+      </c>
+      <c r="C18" s="14">
+        <v>50</v>
+      </c>
+      <c r="D18" s="14">
+        <v>60</v>
+      </c>
+      <c r="E18" s="14">
+        <v>60</v>
+      </c>
+      <c r="F18" s="14">
+        <v>250</v>
+      </c>
+      <c r="G18" s="14">
+        <v>5</v>
+      </c>
+      <c r="H18" s="14">
+        <v>80</v>
+      </c>
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J18" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L18" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="M18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91A70D7-3656-47DE-AFD9-1AF7E835247F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73CCDB1-FE6D-4704-BD15-C2D707DF50E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -1628,26 +1628,50 @@
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="13"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15" t="str">
+      <c r="A19" s="13">
+        <v>46267</v>
+      </c>
+      <c r="B19" s="14">
+        <v>480</v>
+      </c>
+      <c r="C19" s="14">
+        <v>40</v>
+      </c>
+      <c r="D19" s="14">
+        <v>60</v>
+      </c>
+      <c r="E19" s="14">
+        <v>50</v>
+      </c>
+      <c r="F19" s="14">
+        <v>250</v>
+      </c>
+      <c r="G19" s="14">
+        <v>5</v>
+      </c>
+      <c r="H19" s="14">
+        <v>70</v>
+      </c>
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J19" s="15" t="str">
+        <v>950</v>
+      </c>
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" s="16"/>
-      <c r="N19" s="17"/>
+        <v>490</v>
+      </c>
+      <c r="K19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L19" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="M19" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="N19" s="17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C73CCDB1-FE6D-4704-BD15-C2D707DF50E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D67C0E-3FE7-4226-86ED-86FE33572F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -193,9 +193,6 @@
     <t>MCA   section-D1P2635</t>
   </si>
   <si>
-    <t>August</t>
-  </si>
-  <si>
     <t>IT was a hectic day.</t>
   </si>
   <si>
@@ -251,6 +248,12 @@
   </si>
   <si>
     <t xml:space="preserve">An average day </t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>feeling  tired and stressed</t>
   </si>
 </sst>
 </file>
@@ -963,7 +966,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1072,7 +1075,7 @@
         <v>51</v>
       </c>
       <c r="N6" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1109,16 +1112,16 @@
         <v>560</v>
       </c>
       <c r="K7" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L7" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="M7" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="M7" s="16" t="s">
-        <v>59</v>
-      </c>
       <c r="N7" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1155,16 +1158,16 @@
         <v>950</v>
       </c>
       <c r="K8" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L8" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="M8" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="N8" s="17" t="s">
         <v>62</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1201,16 +1204,16 @@
         <v>940</v>
       </c>
       <c r="K9" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="M9" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M9" s="16" t="s">
-        <v>62</v>
-      </c>
       <c r="N9" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -1247,16 +1250,16 @@
         <v>790</v>
       </c>
       <c r="K10" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="M10" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M10" s="16" t="s">
-        <v>62</v>
-      </c>
       <c r="N10" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -1299,10 +1302,10 @@
         <v>50</v>
       </c>
       <c r="M11" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -1339,16 +1342,16 @@
         <v>710</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L12" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M12" s="16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -1394,12 +1397,12 @@
         <v>51</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B14" s="14">
         <v>350</v>
@@ -1431,16 +1434,16 @@
         <v>700</v>
       </c>
       <c r="K14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L14" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M14" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="L14" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="M14" s="16" t="s">
-        <v>59</v>
-      </c>
       <c r="N14" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -1477,16 +1480,16 @@
         <v>870</v>
       </c>
       <c r="K15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L15" s="16" t="s">
+      <c r="M15" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M15" s="16" t="s">
-        <v>62</v>
-      </c>
       <c r="N15" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -1523,16 +1526,16 @@
         <v>760</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L16" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>71</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -1578,7 +1581,7 @@
         <v>51</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -1615,16 +1618,16 @@
         <v>580</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -1661,39 +1664,63 @@
         <v>490</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L19" s="16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M19" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N19" s="17" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A20" s="13">
+        <v>46268</v>
+      </c>
+      <c r="B20" s="14">
+        <v>300</v>
+      </c>
+      <c r="C20" s="14">
         <v>70</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="13"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15" t="str">
+      <c r="D20" s="14">
+        <v>50</v>
+      </c>
+      <c r="E20" s="14">
+        <v>80</v>
+      </c>
+      <c r="F20" s="14">
+        <v>300</v>
+      </c>
+      <c r="G20" s="14">
+        <v>6</v>
+      </c>
+      <c r="H20" s="14">
+        <v>80</v>
+      </c>
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J20" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M20" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="13"/>

--- a/excel file.xlsx
+++ b/excel file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D67C0E-3FE7-4226-86ED-86FE33572F52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7CD66C-84B8-47AA-8ECC-EA22FA1C659F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="77">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -254,6 +254,9 @@
   </si>
   <si>
     <t>feeling  tired and stressed</t>
+  </si>
+  <si>
+    <t>today I met my mother</t>
   </si>
 </sst>
 </file>
@@ -1723,26 +1726,50 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="13"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15" t="str">
+      <c r="A21" s="13">
+        <v>46269</v>
+      </c>
+      <c r="B21" s="14">
+        <v>240</v>
+      </c>
+      <c r="C21" s="14">
+        <v>120</v>
+      </c>
+      <c r="D21" s="14">
+        <v>70</v>
+      </c>
+      <c r="E21" s="14">
+        <v>50</v>
+      </c>
+      <c r="F21" s="14">
+        <v>250</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5</v>
+      </c>
+      <c r="H21" s="14">
+        <v>90</v>
+      </c>
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J21" s="15" t="str">
+        <v>820</v>
+      </c>
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" s="16"/>
-      <c r="N21" s="17"/>
+        <v>620</v>
+      </c>
+      <c r="K21" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="M21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="N21" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="13"/>
